--- a/data/earthworm data_2015.xlsx
+++ b/data/earthworm data_2015.xlsx
@@ -1,32 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erin\Desktop\datafiles_finland field2015\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Documents\GitHub\finland_ew_time_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069E4932-8BF9-4160-862A-4F15EE7E891B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9372"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
-    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Cristina</author>
   </authors>
   <commentList>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -51,7 +63,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH1" authorId="0" shapeId="0">
+    <comment ref="AH1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -67,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AN110" authorId="0" shapeId="0">
+    <comment ref="AN110" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -91,7 +103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AT133" authorId="0" shapeId="0">
+    <comment ref="AT133" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -116,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AT143" authorId="0" shapeId="0">
+    <comment ref="AT143" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -2254,7 +2266,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
@@ -2386,9 +2398,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2426,9 +2438,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2463,7 +2475,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2498,7 +2510,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2671,7 +2683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AU523"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -72907,22 +72919,4 @@
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="300" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>